--- a/docs/candidate-roster-template.xlsx
+++ b/docs/candidate-roster-template.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S500"/>
+  <dimension ref="A1:T500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,8 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -674,6 +675,11 @@
       </c>
       <c r="S1" s="2" t="inlineStr">
         <is>
+          <t>departments</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -764,6 +770,11 @@
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>Tipp Consulting | Tipp Construction</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Strong on D365 Finance. Prefers Gauteng-based work.</t>
         </is>
@@ -2283,7 +2294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2749,73 +2760,95 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
+          <t>departments</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Only here</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>The business units this person is filed under, separated by a pipe; more than one is fine. One of: Tipp Consulting, Tipp Resourcing, Tipp Human Capital, Tipp Construction. Blank files them under the department given when the file is imported, or nowhere. A label and a default filter, not a wall: every department can still bid them.</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Tipp Consulting | Tipp Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Only here</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>Anything a resourcing conversation needs. Free text.</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Strong on D365 Finance. Prefers Gauteng-based work.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Three things that cause trouble</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="68" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>Role names decide everything</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>current_role is compared against the role on a tender seat. It scores full marks for an exact match and nothing at all for a spelling the system does not know, and role is 35 of the 100 matching points. Somebody entered as 'Snr BA' will never come up as a strong match for a Business Analyst seat, and nothing on screen will explain why. Write the role out.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="68" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>Dates must read 2027-03-01</t>
+          <t>Role names decide everything</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Year, then month, then day. Only available_from is a date, and only for people who are committed right now.</t>
+          <t>current_role is compared against the role on a tender seat. It scores full marks for an exact match and nothing at all for a spelling the system does not know, and role is 35 of the 100 matching points. Somebody entered as 'Snr BA' will never come up as a strong match for a Business Analyst seat, and nothing on screen will explain why. Write the role out.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="68" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>Dates must read 2027-03-01</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Year, then month, then day. Only available_from is a date, and only for people who are committed right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="68" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>Use a pipe between list items</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Every list column separates with a pipe, not a comma, so a qualification like 'BCom Information Systems, Cum Laude' stays as one thing.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>When it is filled in: save as CSV (File, Save As, CSV UTF-8) and send that. It is read with  npx tsx scripts/import-candidates.ts &lt;file.csv&gt;  which prints back exactly what it would do and writes nothing. Only a second run with --apply writes. For anybody who already has a CV on file, it fills in a blank column and never overwrites what the CV said, and the report names every column it left alone.</t>
         </is>
@@ -2824,13 +2857,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C28:D28"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
